--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>EquipConfig.xlsx</t>
+  </si>
+  <si>
+    <t>ExpConfigCategory</t>
+  </si>
+  <si>
+    <t>ExpConfig</t>
+  </si>
+  <si>
+    <t>ExpConfig.xlsx</t>
   </si>
   <si>
     <t>GlobalValueConfigCategory</t>
@@ -1145,7 +1154,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1386,6 +1395,20 @@
         <v>57</v>
       </c>
     </row>
+    <row r="13" customFormat="1" spans="2:5">
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -131,6 +131,24 @@
     <t>AIConfig.xlsx</t>
   </si>
   <si>
+    <t>BattleLevelConfigCategory</t>
+  </si>
+  <si>
+    <t>BattleLevelConfig</t>
+  </si>
+  <si>
+    <t>BattleLevelConfig.xlsx</t>
+  </si>
+  <si>
+    <t>BattleWaveConfigCategory</t>
+  </si>
+  <si>
+    <t>BattleWaveConfig</t>
+  </si>
+  <si>
+    <t>BattleWaveConfig.xlsx</t>
+  </si>
+  <si>
     <t>BuffConfigCategory</t>
   </si>
   <si>
@@ -192,6 +210,15 @@
   </si>
   <si>
     <t>ItemConfig.xlsx</t>
+  </si>
+  <si>
+    <t>MonsterBatchConfigCategory</t>
+  </si>
+  <si>
+    <t>MonsterBatchConfig</t>
+  </si>
+  <si>
+    <t>MonsterBatchConfig.xlsx</t>
   </si>
   <si>
     <t>MonsterConfigCategory</t>
@@ -1154,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1283,7 +1310,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" customFormat="1" spans="2:5">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -1311,7 +1338,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:5">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>40</v>
       </c>
@@ -1407,6 +1434,48 @@
       </c>
       <c r="E13" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="2:5">
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="2:5">
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="2:5">
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="22185" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,24 +131,6 @@
     <t>AIConfig.xlsx</t>
   </si>
   <si>
-    <t>BattleLevelConfigCategory</t>
-  </si>
-  <si>
-    <t>BattleLevelConfig</t>
-  </si>
-  <si>
-    <t>BattleLevelConfig.xlsx</t>
-  </si>
-  <si>
-    <t>BattleWaveConfigCategory</t>
-  </si>
-  <si>
-    <t>BattleWaveConfig</t>
-  </si>
-  <si>
-    <t>BattleWaveConfig.xlsx</t>
-  </si>
-  <si>
     <t>BuffConfigCategory</t>
   </si>
   <si>
@@ -203,6 +185,15 @@
     <t>HeroConfig.xlsx</t>
   </si>
   <si>
+    <t>LevelConfigCategory</t>
+  </si>
+  <si>
+    <t>LevelConfig</t>
+  </si>
+  <si>
+    <t>LevelConfig.xlsx</t>
+  </si>
+  <si>
     <t>ItemConfigCategory</t>
   </si>
   <si>
@@ -237,6 +228,15 @@
   </si>
   <si>
     <t>SkillConfig.xlsx</t>
+  </si>
+  <si>
+    <t>WaveConfigCategory</t>
+  </si>
+  <si>
+    <t>WaveConfig</t>
+  </si>
+  <si>
+    <t>WaveConfig.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1310,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:5">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" customFormat="1" spans="2:5">
       <c r="B7" t="s">
         <v>40</v>
       </c>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9555"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -228,6 +228,15 @@
   </si>
   <si>
     <t>SkillConfig.xlsx</t>
+  </si>
+  <si>
+    <t>TaskConfigCategory</t>
+  </si>
+  <si>
+    <t>TaskConfig</t>
+  </si>
+  <si>
+    <t>TaskConfig.xlsx</t>
   </si>
   <si>
     <t>WaveConfigCategory</t>
@@ -1181,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1478,6 +1487,20 @@
         <v>69</v>
       </c>
     </row>
+    <row r="17" customFormat="1" spans="2:5">
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -201,15 +201,6 @@
   </si>
   <si>
     <t>ItemConfig.xlsx</t>
-  </si>
-  <si>
-    <t>MonsterBatchConfigCategory</t>
-  </si>
-  <si>
-    <t>MonsterBatchConfig</t>
-  </si>
-  <si>
-    <t>MonsterBatchConfig.xlsx</t>
   </si>
   <si>
     <t>MonsterConfigCategory</t>
@@ -1190,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1487,20 +1478,6 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="2:5">
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>AIConfig.xlsx</t>
+  </si>
+  <si>
+    <t>DropConfigCategory</t>
+  </si>
+  <si>
+    <t>DropConfig</t>
+  </si>
+  <si>
+    <t>DropConfig.xlsx</t>
   </si>
   <si>
     <t>BuffConfigCategory</t>
@@ -1181,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1324,7 +1333,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:5">
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -1476,6 +1485,20 @@
       </c>
       <c r="E16" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="2:5">
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>MonsterConfig.xlsx</t>
+  </si>
+  <si>
+    <t>NPCConfigCategory</t>
+  </si>
+  <si>
+    <t>NPCConfig</t>
+  </si>
+  <si>
+    <t>NPCConfig.xlsx</t>
   </si>
   <si>
     <t>SkillConfigCategory</t>
@@ -1190,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1501,6 +1510,20 @@
         <v>72</v>
       </c>
     </row>
+    <row r="18" customFormat="1" spans="2:5">
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -237,6 +237,15 @@
   </si>
   <si>
     <t>SkillConfig.xlsx</t>
+  </si>
+  <si>
+    <t>StoreItemConfigCategory</t>
+  </si>
+  <si>
+    <t>StoreItemConfig</t>
+  </si>
+  <si>
+    <t>StoreItemConfig.xlsx</t>
   </si>
   <si>
     <t>TaskConfigCategory</t>
@@ -1199,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1524,6 +1533,20 @@
         <v>75</v>
       </c>
     </row>
+    <row r="19" customFormat="1" spans="2:5">
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>AIConfig.xlsx</t>
+  </si>
+  <si>
+    <t>ArchiveRewardConfigCategory</t>
+  </si>
+  <si>
+    <t>ArchiveRewardConfig</t>
+  </si>
+  <si>
+    <t>ArchiveRewardConfig.xlsx</t>
   </si>
   <si>
     <t>DropConfigCategory</t>
@@ -1208,11 +1217,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="29.8833333333333" customWidth="1"/>
     <col min="6" max="6" width="42.3833333333333" customWidth="1"/>
@@ -1365,7 +1374,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:5">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>40</v>
       </c>
@@ -1545,6 +1554,20 @@
       </c>
       <c r="E19" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="2:5">
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -120,6 +120,24 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>AchievementConfigCategory</t>
+  </si>
+  <si>
+    <t>AchievementConfig</t>
+  </si>
+  <si>
+    <t>AchievementConfig.xlsx</t>
+  </si>
+  <si>
+    <t>AchievementRewardConfigCategory</t>
+  </si>
+  <si>
+    <t>AchievementRewardConfig</t>
+  </si>
+  <si>
+    <t>AchievementRewardConfig.xlsx</t>
   </si>
   <si>
     <t>AIConfigCategory</t>
@@ -1217,12 +1235,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="3" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="29.8833333333333" customWidth="1"/>
     <col min="6" max="6" width="42.3833333333333" customWidth="1"/>
     <col min="7" max="9" width="18" customWidth="1"/>
@@ -1346,7 +1363,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" customFormat="1" spans="2:5">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -1360,7 +1377,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" customFormat="1" spans="2:5">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -1388,7 +1405,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="2:5">
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
         <v>43</v>
       </c>
@@ -1402,7 +1419,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="2:5">
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -1568,6 +1585,34 @@
       </c>
       <c r="E20" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="2:5">
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="2:5">
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -255,6 +255,15 @@
   </si>
   <si>
     <t>NPCConfig.xlsx</t>
+  </si>
+  <si>
+    <t>RechargePointsRewardConfigCategory</t>
+  </si>
+  <si>
+    <t>RechargePointsRewardConfig</t>
+  </si>
+  <si>
+    <t>RechargePointsRewardConfig.xlsx</t>
   </si>
   <si>
     <t>SkillConfigCategory</t>
@@ -1235,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1288,7 +1297,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1323,7 +1332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="57" spans="1:12">
+    <row r="3" s="2" customFormat="1" ht="57" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1349,7 +1358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:13">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -1363,7 +1372,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:5">
+    <row r="5" customFormat="1" spans="1:13">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -1377,7 +1386,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:5">
+    <row r="6" customFormat="1" spans="1:13">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -1391,7 +1400,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:13">
       <c r="B7" t="s">
         <v>40</v>
       </c>
@@ -1405,7 +1414,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="1:13">
       <c r="B8" t="s">
         <v>43</v>
       </c>
@@ -1419,7 +1428,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:13">
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -1433,7 +1442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="2:5">
+    <row r="10" customFormat="1" spans="1:13">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1447,7 +1456,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="2:5">
+    <row r="11" customFormat="1" spans="1:13">
       <c r="B11" t="s">
         <v>52</v>
       </c>
@@ -1461,7 +1470,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="2:5">
+    <row r="12" customFormat="1" spans="1:13">
       <c r="B12" t="s">
         <v>55</v>
       </c>
@@ -1475,7 +1484,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="2:5">
+    <row r="13" customFormat="1" spans="1:13">
       <c r="B13" t="s">
         <v>58</v>
       </c>
@@ -1489,7 +1498,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="2:5">
+    <row r="14" customFormat="1" spans="1:13">
       <c r="B14" t="s">
         <v>61</v>
       </c>
@@ -1503,7 +1512,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="2:5">
+    <row r="15" customFormat="1" spans="1:13">
       <c r="B15" t="s">
         <v>64</v>
       </c>
@@ -1517,7 +1526,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="2:5">
+    <row r="16" customFormat="1" spans="1:13">
       <c r="B16" t="s">
         <v>67</v>
       </c>
@@ -1613,6 +1622,20 @@
       </c>
       <c r="E22" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="2:5">
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -165,6 +165,15 @@
   </si>
   <si>
     <t>DropConfig.xlsx</t>
+  </si>
+  <si>
+    <t>BattlePassConfigCategory</t>
+  </si>
+  <si>
+    <t>BattlePassConfig</t>
+  </si>
+  <si>
+    <t>BattlePassConfig.xlsx</t>
   </si>
   <si>
     <t>BuffConfigCategory</t>
@@ -1244,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1442,7 +1451,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:13">
+    <row r="10" spans="1:13">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1636,6 +1645,20 @@
       </c>
       <c r="E23" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="2:5">
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
@@ -264,6 +264,15 @@
   </si>
   <si>
     <t>NPCConfig.xlsx</t>
+  </si>
+  <si>
+    <t>RechargeConfigCategory</t>
+  </si>
+  <si>
+    <t>RechargeConfig</t>
+  </si>
+  <si>
+    <t>RechargeConfig.xlsx</t>
   </si>
   <si>
     <t>RechargePointsRewardConfigCategory</t>
@@ -1253,7 +1262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1306,7 +1315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:13">
+    <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1341,7 +1350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="57" spans="1:13">
+    <row r="3" s="2" customFormat="1" ht="57" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1367,7 +1376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -1381,7 +1390,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:13">
+    <row r="5" customFormat="1" spans="2:5">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -1395,7 +1404,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:13">
+    <row r="6" customFormat="1" spans="2:5">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -1409,7 +1418,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>40</v>
       </c>
@@ -1423,7 +1432,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
         <v>43</v>
       </c>
@@ -1437,7 +1446,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -1451,7 +1460,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="2:5">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1465,7 +1474,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:13">
+    <row r="11" customFormat="1" spans="2:5">
       <c r="B11" t="s">
         <v>52</v>
       </c>
@@ -1479,7 +1488,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:13">
+    <row r="12" customFormat="1" spans="2:5">
       <c r="B12" t="s">
         <v>55</v>
       </c>
@@ -1493,7 +1502,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:13">
+    <row r="13" customFormat="1" spans="2:5">
       <c r="B13" t="s">
         <v>58</v>
       </c>
@@ -1507,7 +1516,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:13">
+    <row r="14" customFormat="1" spans="2:5">
       <c r="B14" t="s">
         <v>61</v>
       </c>
@@ -1521,7 +1530,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:13">
+    <row r="15" customFormat="1" spans="2:5">
       <c r="B15" t="s">
         <v>64</v>
       </c>
@@ -1535,7 +1544,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:13">
+    <row r="16" customFormat="1" spans="2:5">
       <c r="B16" t="s">
         <v>67</v>
       </c>
@@ -1659,6 +1668,20 @@
       </c>
       <c r="E24" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="2:5">
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>##var</t>
   </si>
@@ -255,6 +255,15 @@
   </si>
   <si>
     <t>MonsterConfig.xlsx</t>
+  </si>
+  <si>
+    <t>MonthSignInConfigCategory</t>
+  </si>
+  <si>
+    <t>MonthSignInConfig</t>
+  </si>
+  <si>
+    <t>MonthSignInConfig.xlsx</t>
   </si>
   <si>
     <t>NPCConfigCategory</t>
@@ -1262,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1315,7 +1324,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1350,7 +1359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="57" spans="1:12">
+    <row r="3" s="2" customFormat="1" ht="57" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -1376,7 +1385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:13">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -1390,7 +1399,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:5">
+    <row r="5" customFormat="1" spans="1:13">
       <c r="B5" t="s">
         <v>34</v>
       </c>
@@ -1404,7 +1413,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:5">
+    <row r="6" customFormat="1" spans="1:13">
       <c r="B6" t="s">
         <v>37</v>
       </c>
@@ -1418,7 +1427,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:13">
       <c r="B7" t="s">
         <v>40</v>
       </c>
@@ -1432,7 +1441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="1:13">
       <c r="B8" t="s">
         <v>43</v>
       </c>
@@ -1446,7 +1455,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:13">
       <c r="B9" t="s">
         <v>46</v>
       </c>
@@ -1460,7 +1469,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="1:13">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1474,7 +1483,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="2:5">
+    <row r="11" customFormat="1" spans="1:13">
       <c r="B11" t="s">
         <v>52</v>
       </c>
@@ -1488,7 +1497,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="2:5">
+    <row r="12" customFormat="1" spans="1:13">
       <c r="B12" t="s">
         <v>55</v>
       </c>
@@ -1502,7 +1511,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="2:5">
+    <row r="13" customFormat="1" spans="1:13">
       <c r="B13" t="s">
         <v>58</v>
       </c>
@@ -1516,7 +1525,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="2:5">
+    <row r="14" customFormat="1" spans="1:13">
       <c r="B14" t="s">
         <v>61</v>
       </c>
@@ -1530,7 +1539,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="2:5">
+    <row r="15" customFormat="1" spans="1:13">
       <c r="B15" t="s">
         <v>64</v>
       </c>
@@ -1544,7 +1553,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="2:5">
+    <row r="16" customFormat="1" spans="1:13">
       <c r="B16" t="s">
         <v>67</v>
       </c>
@@ -1682,6 +1691,20 @@
       </c>
       <c r="E25" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="2:5">
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/__tables__.xlsx
+++ b/Unity/Assets/Config/Excel/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -291,6 +291,15 @@
   </si>
   <si>
     <t>RechargePointsRewardConfig.xlsx</t>
+  </si>
+  <si>
+    <t>ServerOpenRewardConfigCategory</t>
+  </si>
+  <si>
+    <t>ServerOpenRewardConfig</t>
+  </si>
+  <si>
+    <t>ServerOpenRewardConfig.xlsx</t>
   </si>
   <si>
     <t>SkillConfigCategory</t>
@@ -1271,7 +1280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="33.8833333333333" customWidth="1"/>
@@ -1707,6 +1716,20 @@
         <v>99</v>
       </c>
     </row>
+    <row r="27" customFormat="1" spans="2:5">
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
